--- a/artfynd/A 27490-2024 artfynd.xlsx
+++ b/artfynd/A 27490-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91611975</v>
+        <v>118852267</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477860.2157838171</v>
+        <v>478013</v>
       </c>
       <c r="R2" t="n">
-        <v>7039166.06902282</v>
+        <v>7039548</v>
       </c>
       <c r="S2" t="n">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,31 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118852267</v>
+        <v>118852220</v>
       </c>
       <c r="B3" t="n">
-        <v>86829</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478013</v>
+        <v>478112</v>
       </c>
       <c r="R3" t="n">
-        <v>7039548</v>
+        <v>7039463</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118852260</v>
+        <v>118852237</v>
       </c>
       <c r="B4" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478047</v>
+        <v>477837</v>
       </c>
       <c r="R4" t="n">
-        <v>7038924</v>
+        <v>7039492</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118852237</v>
+        <v>91611975</v>
       </c>
       <c r="B5" t="n">
-        <v>90956</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477837</v>
+        <v>477860</v>
       </c>
       <c r="R5" t="n">
-        <v>7039492</v>
+        <v>7039166</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1065,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,27 +1051,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118852220</v>
+        <v>118852231</v>
       </c>
       <c r="B6" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,34 +1078,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478112</v>
+        <v>478030</v>
       </c>
       <c r="R6" t="n">
-        <v>7039463</v>
+        <v>7039541</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,6 +1142,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,15 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118852231</v>
+        <v>118852232</v>
       </c>
       <c r="B7" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,10 +1212,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478030</v>
+        <v>478081</v>
       </c>
       <c r="R7" t="n">
-        <v>7039541</v>
+        <v>7039147</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,7 +1252,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,15 +1279,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118852232</v>
+        <v>118852233</v>
       </c>
       <c r="B8" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478081</v>
+        <v>477900</v>
       </c>
       <c r="R8" t="n">
-        <v>7039147</v>
+        <v>7038694</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,7 +1358,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1418,117 +1382,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>118852233</v>
-      </c>
-      <c r="B9" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>477900</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7038694</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Rödön</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27490-2024 artfynd.xlsx
+++ b/artfynd/A 27490-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852267</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852220</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852237</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1062,6 +1082,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91611975</t>
         </is>
       </c>
     </row>
@@ -1170,6 +1195,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852231</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1276,6 +1306,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852232</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1382,8 +1417,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852233</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>